--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129616604</v>
+        <v>129613982</v>
       </c>
       <c r="B2" t="n">
-        <v>79689</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621230</v>
+        <v>621118</v>
       </c>
       <c r="R2" t="n">
-        <v>7054985</v>
+        <v>7055302</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129616593</v>
+        <v>129616604</v>
       </c>
       <c r="B3" t="n">
-        <v>78827</v>
+        <v>79694</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621232</v>
+        <v>621230</v>
       </c>
       <c r="R3" t="n">
-        <v>7055035</v>
+        <v>7054985</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,49 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129613982</v>
+        <v>129616593</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>78832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621118</v>
+        <v>621232</v>
       </c>
       <c r="R4" t="n">
-        <v>7055302</v>
+        <v>7055035</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -970,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129616783</v>
+        <v>129615701</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621196</v>
+        <v>621133</v>
       </c>
       <c r="R5" t="n">
-        <v>7055053</v>
+        <v>7054991</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1055,61 +1059,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129615701</v>
+        <v>129616783</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621133</v>
+        <v>621196</v>
       </c>
       <c r="R6" t="n">
-        <v>7054991</v>
+        <v>7055053</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1156,12 +1156,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
         <v>129614936</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129617249</v>
+        <v>129616534</v>
       </c>
       <c r="B8" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621030</v>
+        <v>621206</v>
       </c>
       <c r="R8" t="n">
-        <v>7055161</v>
+        <v>7054973</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack tall</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,10 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129615106</v>
+        <v>129617249</v>
       </c>
       <c r="B9" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621150</v>
+        <v>621030</v>
       </c>
       <c r="R9" t="n">
-        <v>7055052</v>
+        <v>7055161</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Färska ringhack tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,10 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129616534</v>
+        <v>129615106</v>
       </c>
       <c r="B10" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621206</v>
+        <v>621150</v>
       </c>
       <c r="R10" t="n">
-        <v>7054973</v>
+        <v>7055052</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129616203</v>
+        <v>129617093</v>
       </c>
       <c r="B11" t="n">
-        <v>80203</v>
+        <v>91551</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1597,21 +1597,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1621,13 +1621,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621203</v>
+        <v>621181</v>
       </c>
       <c r="R11" t="n">
-        <v>7054986</v>
+        <v>7055199</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1671,64 +1671,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129614175</v>
+        <v>129616203</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>80208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621141</v>
+        <v>621203</v>
       </c>
       <c r="R12" t="n">
-        <v>7055354</v>
+        <v>7054986</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1772,22 +1768,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129617046</v>
+        <v>129614175</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1814,7 +1810,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1823,10 +1819,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621194</v>
+        <v>621141</v>
       </c>
       <c r="R13" t="n">
-        <v>7055172</v>
+        <v>7055354</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,45 +1881,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129617093</v>
+        <v>129617046</v>
       </c>
       <c r="B14" t="n">
-        <v>91545</v>
+        <v>98768</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621181</v>
+        <v>621194</v>
       </c>
       <c r="R14" t="n">
-        <v>7055199</v>
+        <v>7055172</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1985,7 +1985,7 @@
         <v>129612716</v>
       </c>
       <c r="B15" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>129615539</v>
       </c>
       <c r="B16" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129615269</v>
       </c>
       <c r="B17" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2292,10 +2292,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129616217</v>
+        <v>129615922</v>
       </c>
       <c r="B18" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621204</v>
+        <v>621177</v>
       </c>
       <c r="R18" t="n">
-        <v>7054990</v>
+        <v>7054963</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129615922</v>
+        <v>129616217</v>
       </c>
       <c r="B19" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621177</v>
+        <v>621204</v>
       </c>
       <c r="R19" t="n">
-        <v>7054963</v>
+        <v>7054990</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2509,7 +2509,7 @@
         <v>129615034</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>129616723</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>129615233</v>
       </c>
       <c r="B22" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>129615702</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>129616405</v>
       </c>
       <c r="B24" t="n">
-        <v>58363</v>
+        <v>58368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129613982</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129616604</v>
       </c>
       <c r="B3" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>129616593</v>
       </c>
       <c r="B4" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129615701</v>
+        <v>129616783</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621133</v>
+        <v>621196</v>
       </c>
       <c r="R5" t="n">
-        <v>7054991</v>
+        <v>7055053</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,57 +1055,61 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129616783</v>
+        <v>129615701</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621196</v>
+        <v>621133</v>
       </c>
       <c r="R6" t="n">
-        <v>7055053</v>
+        <v>7054991</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1156,12 +1156,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
         <v>129614936</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>129616534</v>
       </c>
       <c r="B8" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129617249</v>
       </c>
       <c r="B9" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>129615106</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>129617093</v>
       </c>
       <c r="B11" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>129616203</v>
       </c>
       <c r="B12" t="n">
-        <v>80208</v>
+        <v>80209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>129614175</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>129617046</v>
       </c>
       <c r="B14" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>129612716</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>129615539</v>
       </c>
       <c r="B16" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2191,37 +2191,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129615269</v>
+        <v>129615922</v>
       </c>
       <c r="B17" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2230,10 +2231,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>621115</v>
+        <v>621177</v>
       </c>
       <c r="R17" t="n">
-        <v>7055038</v>
+        <v>7054963</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2266,6 +2267,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2292,10 +2298,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129615922</v>
+        <v>129616217</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,10 +2338,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621177</v>
+        <v>621204</v>
       </c>
       <c r="R18" t="n">
-        <v>7054963</v>
+        <v>7054990</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2399,38 +2405,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129616217</v>
+        <v>129615269</v>
       </c>
       <c r="B19" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2439,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621204</v>
+        <v>621115</v>
       </c>
       <c r="R19" t="n">
-        <v>7054990</v>
+        <v>7055038</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2475,11 +2480,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,7 +2509,7 @@
         <v>129615034</v>
       </c>
       <c r="B20" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>129616723</v>
       </c>
       <c r="B21" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>129615233</v>
       </c>
       <c r="B22" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>129615702</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>129616405</v>
       </c>
       <c r="B24" t="n">
-        <v>58368</v>
+        <v>58369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129613982</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129616604</v>
+        <v>129616593</v>
       </c>
       <c r="B3" t="n">
-        <v>79695</v>
+        <v>78838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621230</v>
+        <v>621232</v>
       </c>
       <c r="R3" t="n">
-        <v>7054985</v>
+        <v>7055035</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -873,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129616593</v>
+        <v>129616604</v>
       </c>
       <c r="B4" t="n">
-        <v>78833</v>
+        <v>79700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621232</v>
+        <v>621230</v>
       </c>
       <c r="R4" t="n">
-        <v>7055035</v>
+        <v>7054985</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -973,7 +973,7 @@
         <v>129616783</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>129615701</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129614936</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617093</v>
+        <v>129616203</v>
       </c>
       <c r="B11" t="n">
-        <v>91552</v>
+        <v>80214</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1597,21 +1597,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1621,13 +1621,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621181</v>
+        <v>621203</v>
       </c>
       <c r="R11" t="n">
-        <v>7055199</v>
+        <v>7054986</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1671,22 +1671,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129616203</v>
+        <v>129617093</v>
       </c>
       <c r="B12" t="n">
-        <v>80209</v>
+        <v>91557</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621203</v>
+        <v>621181</v>
       </c>
       <c r="R12" t="n">
-        <v>7054986</v>
+        <v>7055199</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1768,12 +1768,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1783,7 +1783,7 @@
         <v>129614175</v>
       </c>
       <c r="B13" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>129617046</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,38 +2191,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129615922</v>
+        <v>129615269</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2231,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>621177</v>
+        <v>621115</v>
       </c>
       <c r="R17" t="n">
-        <v>7054963</v>
+        <v>7055038</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2267,11 +2266,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,7 +2292,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129616217</v>
+        <v>129615922</v>
       </c>
       <c r="B18" t="n">
         <v>57736</v>
@@ -2338,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621204</v>
+        <v>621177</v>
       </c>
       <c r="R18" t="n">
-        <v>7054990</v>
+        <v>7054963</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2405,37 +2399,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129615269</v>
+        <v>129616217</v>
       </c>
       <c r="B19" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2444,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621115</v>
+        <v>621204</v>
       </c>
       <c r="R19" t="n">
-        <v>7055038</v>
+        <v>7054990</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2480,6 +2475,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2509,7 +2509,7 @@
         <v>129615034</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>129615233</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>129615702</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129613982</v>
+        <v>129616604</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>79700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621118</v>
+        <v>621230</v>
       </c>
       <c r="R2" t="n">
-        <v>7055302</v>
+        <v>7054985</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -873,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129616604</v>
+        <v>129613982</v>
       </c>
       <c r="B4" t="n">
-        <v>79700</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621230</v>
+        <v>621118</v>
       </c>
       <c r="R4" t="n">
-        <v>7054985</v>
+        <v>7055302</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1372,7 +1372,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129617249</v>
+        <v>129615106</v>
       </c>
       <c r="B9" t="n">
         <v>57736</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621030</v>
+        <v>621150</v>
       </c>
       <c r="R9" t="n">
-        <v>7055161</v>
+        <v>7055052</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack tall</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,7 +1479,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129615106</v>
+        <v>129617249</v>
       </c>
       <c r="B10" t="n">
         <v>57736</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621150</v>
+        <v>621030</v>
       </c>
       <c r="R10" t="n">
-        <v>7055052</v>
+        <v>7055161</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Färska ringhack tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,10 +1586,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129616203</v>
+        <v>129617093</v>
       </c>
       <c r="B11" t="n">
-        <v>80214</v>
+        <v>91557</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1597,21 +1597,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1621,13 +1621,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621203</v>
+        <v>621181</v>
       </c>
       <c r="R11" t="n">
-        <v>7054986</v>
+        <v>7055199</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1671,22 +1671,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617093</v>
+        <v>129616203</v>
       </c>
       <c r="B12" t="n">
-        <v>91557</v>
+        <v>80214</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621181</v>
+        <v>621203</v>
       </c>
       <c r="R12" t="n">
-        <v>7055199</v>
+        <v>7054986</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1768,12 +1768,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129612716</v>
+        <v>129615539</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,27 +1993,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621022</v>
+        <v>621123</v>
       </c>
       <c r="R15" t="n">
-        <v>7055181</v>
+        <v>7054972</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2060,11 +2060,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2077,22 +2072,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129615539</v>
+        <v>129612716</v>
       </c>
       <c r="B16" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,27 +2095,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2129,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621123</v>
+        <v>621022</v>
       </c>
       <c r="R16" t="n">
-        <v>7054972</v>
+        <v>7055181</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2167,6 +2162,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2179,49 +2179,50 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129615269</v>
+        <v>129615922</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2230,10 +2231,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>621115</v>
+        <v>621177</v>
       </c>
       <c r="R17" t="n">
-        <v>7055038</v>
+        <v>7054963</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2266,6 +2267,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2292,7 +2298,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129615922</v>
+        <v>129616217</v>
       </c>
       <c r="B18" t="n">
         <v>57736</v>
@@ -2332,10 +2338,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621177</v>
+        <v>621204</v>
       </c>
       <c r="R18" t="n">
-        <v>7054963</v>
+        <v>7054990</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2399,38 +2405,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129616217</v>
+        <v>129615269</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2439,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621204</v>
+        <v>621115</v>
       </c>
       <c r="R19" t="n">
-        <v>7054990</v>
+        <v>7055038</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2475,11 +2480,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129616604</v>
+        <v>129613982</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621230</v>
+        <v>621118</v>
       </c>
       <c r="R2" t="n">
-        <v>7054985</v>
+        <v>7055302</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129616593</v>
+        <v>129616604</v>
       </c>
       <c r="B3" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621232</v>
+        <v>621230</v>
       </c>
       <c r="R3" t="n">
-        <v>7055035</v>
+        <v>7054985</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,49 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129613982</v>
+        <v>129616593</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>78838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621118</v>
+        <v>621232</v>
       </c>
       <c r="R4" t="n">
-        <v>7055302</v>
+        <v>7055035</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1372,7 +1372,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129615106</v>
+        <v>129617249</v>
       </c>
       <c r="B9" t="n">
         <v>57736</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621150</v>
+        <v>621030</v>
       </c>
       <c r="R9" t="n">
-        <v>7055052</v>
+        <v>7055161</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Färska ringhack tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,7 +1479,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129617249</v>
+        <v>129615106</v>
       </c>
       <c r="B10" t="n">
         <v>57736</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621030</v>
+        <v>621150</v>
       </c>
       <c r="R10" t="n">
-        <v>7055161</v>
+        <v>7055052</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack tall</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,45 +1586,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617093</v>
+        <v>129614175</v>
       </c>
       <c r="B11" t="n">
-        <v>91557</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621181</v>
+        <v>621141</v>
       </c>
       <c r="R11" t="n">
-        <v>7055199</v>
+        <v>7055354</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1683,10 +1687,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129616203</v>
+        <v>129617093</v>
       </c>
       <c r="B12" t="n">
-        <v>80214</v>
+        <v>91557</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1694,21 +1698,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1718,13 +1722,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621203</v>
+        <v>621181</v>
       </c>
       <c r="R12" t="n">
-        <v>7054986</v>
+        <v>7055199</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1768,64 +1772,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129614175</v>
+        <v>129616203</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>80214</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621141</v>
+        <v>621203</v>
       </c>
       <c r="R13" t="n">
-        <v>7055354</v>
+        <v>7054986</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1869,12 +1869,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -970,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129616783</v>
+        <v>129615701</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621196</v>
+        <v>621133</v>
       </c>
       <c r="R5" t="n">
-        <v>7055053</v>
+        <v>7054991</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1055,61 +1059,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129615701</v>
+        <v>129616783</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621133</v>
+        <v>621196</v>
       </c>
       <c r="R6" t="n">
-        <v>7054991</v>
+        <v>7055053</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1156,12 +1156,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1586,52 +1586,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129614175</v>
+        <v>129616203</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>80214</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621141</v>
+        <v>621203</v>
       </c>
       <c r="R11" t="n">
-        <v>7055354</v>
+        <v>7054986</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1675,12 +1671,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1784,48 +1780,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129616203</v>
+        <v>129614175</v>
       </c>
       <c r="B13" t="n">
-        <v>80214</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621203</v>
+        <v>621141</v>
       </c>
       <c r="R13" t="n">
-        <v>7054986</v>
+        <v>7055354</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1869,12 +1869,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129613982</v>
+        <v>129616604</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>79700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621118</v>
+        <v>621230</v>
       </c>
       <c r="R2" t="n">
-        <v>7055302</v>
+        <v>7054985</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -776,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129616604</v>
+        <v>129616593</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621230</v>
+        <v>621232</v>
       </c>
       <c r="R3" t="n">
-        <v>7054985</v>
+        <v>7055035</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -873,45 +869,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129616593</v>
+        <v>129613982</v>
       </c>
       <c r="B4" t="n">
-        <v>78838</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621232</v>
+        <v>621118</v>
       </c>
       <c r="R4" t="n">
-        <v>7055035</v>
+        <v>7055302</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -970,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129615701</v>
+        <v>129616783</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621133</v>
+        <v>621196</v>
       </c>
       <c r="R5" t="n">
-        <v>7054991</v>
+        <v>7055053</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,57 +1055,61 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129616783</v>
+        <v>129615701</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621196</v>
+        <v>621133</v>
       </c>
       <c r="R6" t="n">
-        <v>7055053</v>
+        <v>7054991</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1156,12 +1156,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1586,48 +1586,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129616203</v>
+        <v>129614175</v>
       </c>
       <c r="B11" t="n">
-        <v>80214</v>
+        <v>98778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621203</v>
+        <v>621141</v>
       </c>
       <c r="R11" t="n">
-        <v>7054986</v>
+        <v>7055354</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1671,57 +1675,61 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617093</v>
+        <v>129617046</v>
       </c>
       <c r="B12" t="n">
-        <v>91557</v>
+        <v>98778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621181</v>
+        <v>621194</v>
       </c>
       <c r="R12" t="n">
-        <v>7055199</v>
+        <v>7055172</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1780,49 +1788,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129614175</v>
+        <v>129617093</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>91561</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621141</v>
+        <v>621181</v>
       </c>
       <c r="R13" t="n">
-        <v>7055354</v>
+        <v>7055199</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1881,52 +1885,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129617046</v>
+        <v>129616203</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>80214</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621194</v>
+        <v>621203</v>
       </c>
       <c r="R14" t="n">
-        <v>7055172</v>
+        <v>7054986</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1970,22 +1970,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129615539</v>
+        <v>129612716</v>
       </c>
       <c r="B15" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,27 +1993,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621123</v>
+        <v>621022</v>
       </c>
       <c r="R15" t="n">
-        <v>7054972</v>
+        <v>7055181</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2060,6 +2060,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2072,22 +2077,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129612716</v>
+        <v>129615539</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2095,27 +2100,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2124,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621022</v>
+        <v>621123</v>
       </c>
       <c r="R16" t="n">
-        <v>7055181</v>
+        <v>7054972</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2162,11 +2167,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2179,50 +2179,49 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129615922</v>
+        <v>129615269</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>98778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2231,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>621177</v>
+        <v>621115</v>
       </c>
       <c r="R17" t="n">
-        <v>7054963</v>
+        <v>7055038</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2267,11 +2266,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,7 +2292,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129616217</v>
+        <v>129615922</v>
       </c>
       <c r="B18" t="n">
         <v>57736</v>
@@ -2338,10 +2332,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621204</v>
+        <v>621177</v>
       </c>
       <c r="R18" t="n">
-        <v>7054990</v>
+        <v>7054963</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2405,37 +2399,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129615269</v>
+        <v>129616217</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2444,10 +2439,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621115</v>
+        <v>621204</v>
       </c>
       <c r="R19" t="n">
-        <v>7055038</v>
+        <v>7054990</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2480,6 +2475,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129613982</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>129615701</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1586,49 +1586,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129614175</v>
+        <v>129617093</v>
       </c>
       <c r="B11" t="n">
-        <v>98778</v>
+        <v>91563</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621141</v>
+        <v>621181</v>
       </c>
       <c r="R11" t="n">
-        <v>7055354</v>
+        <v>7055199</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1687,52 +1683,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617046</v>
+        <v>129616203</v>
       </c>
       <c r="B12" t="n">
-        <v>98778</v>
+        <v>80214</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621194</v>
+        <v>621203</v>
       </c>
       <c r="R12" t="n">
-        <v>7055172</v>
+        <v>7054986</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1776,57 +1768,61 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129617093</v>
+        <v>129614175</v>
       </c>
       <c r="B13" t="n">
-        <v>91561</v>
+        <v>98780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621181</v>
+        <v>621141</v>
       </c>
       <c r="R13" t="n">
-        <v>7055199</v>
+        <v>7055354</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,48 +1881,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129616203</v>
+        <v>129617046</v>
       </c>
       <c r="B14" t="n">
-        <v>80214</v>
+        <v>98780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621203</v>
+        <v>621194</v>
       </c>
       <c r="R14" t="n">
-        <v>7054986</v>
+        <v>7055172</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1970,12 +1970,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2191,37 +2191,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129615269</v>
+        <v>129615922</v>
       </c>
       <c r="B17" t="n">
-        <v>98778</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2230,10 +2231,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>621115</v>
+        <v>621177</v>
       </c>
       <c r="R17" t="n">
-        <v>7055038</v>
+        <v>7054963</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2266,6 +2267,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2292,7 +2298,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129615922</v>
+        <v>129616217</v>
       </c>
       <c r="B18" t="n">
         <v>57736</v>
@@ -2332,10 +2338,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621177</v>
+        <v>621204</v>
       </c>
       <c r="R18" t="n">
-        <v>7054963</v>
+        <v>7054990</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2399,38 +2405,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129616217</v>
+        <v>129615269</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2439,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621204</v>
+        <v>621115</v>
       </c>
       <c r="R19" t="n">
-        <v>7054990</v>
+        <v>7055038</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2475,11 +2480,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -970,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129616783</v>
+        <v>129615701</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621196</v>
+        <v>621133</v>
       </c>
       <c r="R5" t="n">
-        <v>7055053</v>
+        <v>7054991</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1055,61 +1059,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129615701</v>
+        <v>129616783</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621133</v>
+        <v>621196</v>
       </c>
       <c r="R6" t="n">
-        <v>7054991</v>
+        <v>7055053</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1156,12 +1156,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129612716</v>
+        <v>129615539</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,27 +1993,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621022</v>
+        <v>621123</v>
       </c>
       <c r="R15" t="n">
-        <v>7055181</v>
+        <v>7054972</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2060,11 +2060,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2077,22 +2072,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129615539</v>
+        <v>129612716</v>
       </c>
       <c r="B16" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,27 +2095,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2129,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621123</v>
+        <v>621022</v>
       </c>
       <c r="R16" t="n">
-        <v>7054972</v>
+        <v>7055181</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2167,6 +2162,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2179,12 +2179,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -970,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129615701</v>
+        <v>129616783</v>
       </c>
       <c r="B5" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621133</v>
+        <v>621196</v>
       </c>
       <c r="R5" t="n">
-        <v>7054991</v>
+        <v>7055053</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,57 +1055,61 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129616783</v>
+        <v>129615701</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621196</v>
+        <v>621133</v>
       </c>
       <c r="R6" t="n">
-        <v>7055053</v>
+        <v>7054991</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1156,12 +1156,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129613982</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129616783</v>
+        <v>129615701</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621196</v>
+        <v>621133</v>
       </c>
       <c r="R5" t="n">
-        <v>7055053</v>
+        <v>7054991</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1055,61 +1059,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129615701</v>
+        <v>129616783</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621133</v>
+        <v>621196</v>
       </c>
       <c r="R6" t="n">
-        <v>7054991</v>
+        <v>7055053</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1156,12 +1156,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617093</v>
+        <v>129616203</v>
       </c>
       <c r="B11" t="n">
-        <v>91563</v>
+        <v>80214</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1597,21 +1597,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1621,13 +1621,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621181</v>
+        <v>621203</v>
       </c>
       <c r="R11" t="n">
-        <v>7055199</v>
+        <v>7054986</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1671,22 +1671,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129616203</v>
+        <v>129617093</v>
       </c>
       <c r="B12" t="n">
-        <v>80214</v>
+        <v>91563</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621203</v>
+        <v>621181</v>
       </c>
       <c r="R12" t="n">
-        <v>7054986</v>
+        <v>7055199</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1768,22 +1768,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129614175</v>
+        <v>129617046</v>
       </c>
       <c r="B13" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621141</v>
+        <v>621194</v>
       </c>
       <c r="R13" t="n">
-        <v>7055354</v>
+        <v>7055172</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1881,10 +1881,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129617046</v>
+        <v>129614175</v>
       </c>
       <c r="B14" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621194</v>
+        <v>621141</v>
       </c>
       <c r="R14" t="n">
-        <v>7055172</v>
+        <v>7055354</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2408,7 +2408,7 @@
         <v>129615269</v>
       </c>
       <c r="B19" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -1780,7 +1780,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129617046</v>
+        <v>129614175</v>
       </c>
       <c r="B13" t="n">
         <v>98790</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621194</v>
+        <v>621141</v>
       </c>
       <c r="R13" t="n">
-        <v>7055172</v>
+        <v>7055354</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1881,7 +1881,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129614175</v>
+        <v>129617046</v>
       </c>
       <c r="B14" t="n">
         <v>98790</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621141</v>
+        <v>621194</v>
       </c>
       <c r="R14" t="n">
-        <v>7055354</v>
+        <v>7055172</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>

--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129616604</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129616593</v>
       </c>
       <c r="B3" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129613982</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129615701</v>
+        <v>129616783</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621133</v>
+        <v>621196</v>
       </c>
       <c r="R5" t="n">
-        <v>7054991</v>
+        <v>7055053</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,57 +1055,61 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129616783</v>
+        <v>129615701</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621196</v>
+        <v>621133</v>
       </c>
       <c r="R6" t="n">
-        <v>7055053</v>
+        <v>7054991</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1156,12 +1156,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
         <v>129614936</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>129616534</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129617249</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>129615106</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129616203</v>
+        <v>129617093</v>
       </c>
       <c r="B11" t="n">
-        <v>80214</v>
+        <v>91566</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1597,21 +1597,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1621,13 +1621,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621203</v>
+        <v>621181</v>
       </c>
       <c r="R11" t="n">
-        <v>7054986</v>
+        <v>7055199</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1671,22 +1671,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617093</v>
+        <v>129616203</v>
       </c>
       <c r="B12" t="n">
-        <v>91563</v>
+        <v>80217</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621181</v>
+        <v>621203</v>
       </c>
       <c r="R12" t="n">
-        <v>7055199</v>
+        <v>7054986</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1768,12 +1768,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1783,7 +1783,7 @@
         <v>129614175</v>
       </c>
       <c r="B13" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>129617046</v>
       </c>
       <c r="B14" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>129615539</v>
       </c>
       <c r="B15" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>129612716</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>129615922</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>129616217</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>129615269</v>
       </c>
       <c r="B19" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>129615034</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>129616723</v>
       </c>
       <c r="B21" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>129615233</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>129615702</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>129616405</v>
       </c>
       <c r="B24" t="n">
-        <v>58369</v>
+        <v>58372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129616604</v>
       </c>
       <c r="B2" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129616593</v>
       </c>
       <c r="B3" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129613982</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>129616783</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>129615701</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129614936</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>129616534</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129617249</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>129615106</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>129617093</v>
       </c>
       <c r="B11" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,48 +1683,52 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129616203</v>
+        <v>129614175</v>
       </c>
       <c r="B12" t="n">
-        <v>80217</v>
+        <v>98797</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621203</v>
+        <v>621141</v>
       </c>
       <c r="R12" t="n">
-        <v>7054986</v>
+        <v>7055354</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1768,22 +1772,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129614175</v>
+        <v>129617046</v>
       </c>
       <c r="B13" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1810,7 +1814,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1819,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621141</v>
+        <v>621194</v>
       </c>
       <c r="R13" t="n">
-        <v>7055354</v>
+        <v>7055172</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1881,52 +1885,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129617046</v>
+        <v>129616203</v>
       </c>
       <c r="B14" t="n">
-        <v>98794</v>
+        <v>80220</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621194</v>
+        <v>621203</v>
       </c>
       <c r="R14" t="n">
-        <v>7055172</v>
+        <v>7054986</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1970,22 +1970,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129615539</v>
+        <v>129612716</v>
       </c>
       <c r="B15" t="n">
-        <v>57895</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,27 +1993,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621123</v>
+        <v>621022</v>
       </c>
       <c r="R15" t="n">
-        <v>7054972</v>
+        <v>7055181</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2060,6 +2060,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2072,22 +2077,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129612716</v>
+        <v>129615539</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>57898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2095,27 +2100,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2124,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621022</v>
+        <v>621123</v>
       </c>
       <c r="R16" t="n">
-        <v>7055181</v>
+        <v>7054972</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2162,11 +2167,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2179,12 +2179,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2194,7 +2194,7 @@
         <v>129615922</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>129616217</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>129615269</v>
       </c>
       <c r="B19" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>129615034</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>129616723</v>
       </c>
       <c r="B21" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>129615233</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>129615702</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>129616405</v>
       </c>
       <c r="B24" t="n">
-        <v>58372</v>
+        <v>58375</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -970,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129616783</v>
+        <v>129615701</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621196</v>
+        <v>621133</v>
       </c>
       <c r="R5" t="n">
-        <v>7055053</v>
+        <v>7054991</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1055,61 +1059,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129615701</v>
+        <v>129616783</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621133</v>
+        <v>621196</v>
       </c>
       <c r="R6" t="n">
-        <v>7054991</v>
+        <v>7055053</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1156,12 +1156,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617093</v>
+        <v>129616203</v>
       </c>
       <c r="B11" t="n">
-        <v>91569</v>
+        <v>80220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1597,21 +1597,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1621,13 +1621,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621181</v>
+        <v>621203</v>
       </c>
       <c r="R11" t="n">
-        <v>7055199</v>
+        <v>7054986</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1671,12 +1671,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129616203</v>
+        <v>129617093</v>
       </c>
       <c r="B14" t="n">
-        <v>80220</v>
+        <v>91569</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,13 +1920,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621203</v>
+        <v>621181</v>
       </c>
       <c r="R14" t="n">
-        <v>7054986</v>
+        <v>7055199</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1970,22 +1970,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129612716</v>
+        <v>129615539</v>
       </c>
       <c r="B15" t="n">
-        <v>57740</v>
+        <v>57898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,27 +1993,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621022</v>
+        <v>621123</v>
       </c>
       <c r="R15" t="n">
-        <v>7055181</v>
+        <v>7054972</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2060,11 +2060,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2077,22 +2072,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129615539</v>
+        <v>129612716</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,27 +2095,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2129,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621123</v>
+        <v>621022</v>
       </c>
       <c r="R16" t="n">
-        <v>7054972</v>
+        <v>7055181</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2167,6 +2162,11 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2179,12 +2179,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 44868-2025 artfynd.xlsx
+++ b/artfynd/A 44868-2025 artfynd.xlsx
@@ -970,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129615701</v>
+        <v>129616783</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621133</v>
+        <v>621196</v>
       </c>
       <c r="R5" t="n">
-        <v>7054991</v>
+        <v>7055053</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1059,57 +1055,61 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monika Norberg</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129616783</v>
+        <v>129615701</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Finnbäcken, Finnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621196</v>
+        <v>621133</v>
       </c>
       <c r="R6" t="n">
-        <v>7055053</v>
+        <v>7054991</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1156,12 +1156,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Monika Norberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
